--- a/CryoGrid/CryoGridCommunity_results/templates/automatic_loops/TILE_LOOP_NEXT.xlsx
+++ b/CryoGrid/CryoGridCommunity_results/templates/automatic_loops/TILE_LOOP_NEXT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Utilisateurs\pozsgayv\Documents\CryoGrid_VP_Workflow\CryoGrid\CryoGridCommunity_results\templates\automatic_loops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49BA7308-29E8-4B8A-88E3-1722BC647F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5677AFB1-A863-4AAB-815B-475FA78E93CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11184" yWindow="-17280" windowWidth="15552" windowHeight="16656" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -114,10 +114,10 @@
     <t>save_last_timestep_nloop_loop1_last_timestep.mat</t>
   </si>
   <si>
-    <t>D:\Utilisateurs\pozsgayv\Documents\CryoGrid_VP_Workflow\CryoGrid\CryoGridCommunity_results\templates\save_last_timestep_nloop\</t>
-  </si>
-  <si>
     <t>TILE_1D</t>
+  </si>
+  <si>
+    <t>D:\Utilisateurs\pozsgayv\Documents\CryoGrid_VP_Workflow\CryoGrid\CryoGridCommunity_results\templates\automatic_loops\</t>
   </si>
 </sst>
 </file>
@@ -546,9 +546,9 @@
     </row>
     <row r="5" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="5">
+        <v>26</v>
+      </c>
+      <c r="B5" s="7">
         <v>2</v>
       </c>
     </row>
@@ -566,7 +566,7 @@
         <v>18</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -653,9 +653,9 @@
     </row>
     <row r="19" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="5">
+        <v>26</v>
+      </c>
+      <c r="B19" s="7">
         <v>3</v>
       </c>
     </row>

--- a/CryoGrid/CryoGridCommunity_results/templates/automatic_loops/TILE_LOOP_NEXT.xlsx
+++ b/CryoGrid/CryoGridCommunity_results/templates/automatic_loops/TILE_LOOP_NEXT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Utilisateurs\pozsgayv\Documents\CryoGrid_VP_Workflow\CryoGrid\CryoGridCommunity_results\templates\automatic_loops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5677AFB1-A863-4AAB-815B-475FA78E93CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC6A495-9669-4630-8490-1C7B8BD13F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="27">
   <si>
     <t>-------------------</t>
   </si>
@@ -82,9 +82,6 @@
   </si>
   <si>
     <t>save_timestep</t>
-  </si>
-  <si>
-    <t>timestep that model progress is displayed [days], if empty save final state at the end of the run, so that it can serve as initial condition for new runs</t>
   </si>
   <si>
     <t>restart_OUT_last_timestep</t>
@@ -514,258 +511,244 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A3:E35"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" outlineLevelRow="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.54296875" customWidth="1"/>
     <col min="2" max="2" width="19.54296875" customWidth="1"/>
     <col min="3" max="3" width="18.54296875" customWidth="1"/>
     <col min="4" max="4" width="16.81640625" customWidth="1"/>
-    <col min="5" max="5" width="16.453125" customWidth="1"/>
-    <col min="6" max="6" width="30.54296875" customWidth="1"/>
-    <col min="7" max="7" width="13.453125" customWidth="1"/>
-    <col min="8" max="8" width="30.08984375" customWidth="1"/>
-    <col min="9" max="9" width="21.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="42.26953125" customWidth="1"/>
-    <col min="11" max="11" width="9.7265625" customWidth="1"/>
-    <col min="12" max="12" width="12.1796875" customWidth="1"/>
+    <col min="5" max="5" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="42.26953125" customWidth="1"/>
+    <col min="7" max="7" width="9.7265625" customWidth="1"/>
+    <col min="8" max="8" width="12.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
+    <row r="2" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="5" t="s">
+    <row r="3" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="7">
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+    </row>
+    <row r="7" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+    </row>
+    <row r="11" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+    </row>
+    <row r="12" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+    <row r="13" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="19" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-    </row>
-    <row r="10" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="B19" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>7</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B22" t="s">
         <v>9</v>
       </c>
-      <c r="C10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="C22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="5"/>
-    </row>
-    <row r="11" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+    </row>
+    <row r="23" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>8</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B23" t="s">
         <v>9</v>
       </c>
-      <c r="C11">
+      <c r="C23" s="6">
+        <v>2</v>
+      </c>
+      <c r="D23" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D26" s="2"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" t="s">
         <v>1</v>
       </c>
-      <c r="D11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="5"/>
-    </row>
-    <row r="12" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-    </row>
-    <row r="13" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-    </row>
-    <row r="14" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.35"/>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B18" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" s="5" t="s">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31">
+        <v>5</v>
+      </c>
+      <c r="D31" s="4"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" s="6" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>5</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>7</v>
-      </c>
-      <c r="B24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" t="s">
-        <v>14</v>
-      </c>
-      <c r="D24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E24" s="5"/>
-    </row>
-    <row r="25" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25" t="s">
-        <v>9</v>
-      </c>
-      <c r="C25" s="6">
-        <v>2</v>
-      </c>
-      <c r="D25" t="s">
-        <v>10</v>
-      </c>
-      <c r="E25" s="5"/>
-    </row>
-    <row r="26" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="D28" s="2"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>11</v>
-      </c>
-      <c r="B30" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>14</v>
-      </c>
-      <c r="B31" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D32" s="4"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33">
-        <v>5</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>12</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D34" s="4"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
         <v>2</v>
       </c>
     </row>

--- a/CryoGrid/CryoGridCommunity_results/templates/automatic_loops/TILE_LOOP_NEXT.xlsx
+++ b/CryoGrid/CryoGridCommunity_results/templates/automatic_loops/TILE_LOOP_NEXT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Utilisateurs\pozsgayv\Documents\CryoGrid_VP_Workflow\CryoGrid\CryoGridCommunity_results\templates\automatic_loops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC6A495-9669-4630-8490-1C7B8BD13F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D140B6CE-68D8-439C-9D72-EC57E4BB0839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -114,7 +114,7 @@
     <t>TILE_1D</t>
   </si>
   <si>
-    <t>D:\Utilisateurs\pozsgayv\Documents\CryoGrid_VP_Workflow\CryoGrid\CryoGridCommunity_results\templates\automatic_loops\</t>
+    <t>..\CryoGridCommunity_results\templates\automatic_loops\</t>
   </si>
 </sst>
 </file>

--- a/CryoGrid/CryoGridCommunity_results/templates/automatic_loops/TILE_LOOP_NEXT.xlsx
+++ b/CryoGrid/CryoGridCommunity_results/templates/automatic_loops/TILE_LOOP_NEXT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Utilisateurs\pozsgayv\Documents\CryoGrid_VP_Workflow\CryoGrid\CryoGridCommunity_results\templates\automatic_loops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D140B6CE-68D8-439C-9D72-EC57E4BB0839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADB61598-A92B-4A32-8CD9-43D7CEF2028E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="24">
   <si>
     <t>-------------------</t>
   </si>
@@ -105,32 +105,15 @@
     <t>update_forcing_out</t>
   </si>
   <si>
-    <t>loop2</t>
-  </si>
-  <si>
-    <t>save_last_timestep_nloop_loop1_last_timestep.mat</t>
-  </si>
-  <si>
     <t>TILE_1D</t>
-  </si>
-  <si>
-    <t>..\CryoGridCommunity_results\templates\automatic_loops\</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -144,32 +127,25 @@
       <family val="3"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
+      <color rgb="FF00B0F0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF00B0F0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC00000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -184,19 +160,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -514,241 +488,227 @@
   <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" outlineLevelRow="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.54296875" customWidth="1"/>
-    <col min="2" max="2" width="19.54296875" customWidth="1"/>
-    <col min="3" max="3" width="18.54296875" customWidth="1"/>
-    <col min="4" max="4" width="16.81640625" customWidth="1"/>
-    <col min="5" max="5" width="21.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="42.26953125" customWidth="1"/>
-    <col min="7" max="7" width="9.7265625" customWidth="1"/>
-    <col min="8" max="8" width="12.1796875" customWidth="1"/>
+    <col min="1" max="1" width="23.54296875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="19.54296875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="18.54296875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="16.81640625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="21.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="42.26953125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="9.7265625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="12.1796875" style="3" customWidth="1"/>
+    <col min="9" max="16384" width="8.81640625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="7">
+      <c r="A3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35"/>
     <row r="5" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="A6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
     </row>
     <row r="7" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
     </row>
     <row r="8" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+      <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+      <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="3">
         <v>1</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="A10" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
     </row>
     <row r="11" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+      <c r="A11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
     </row>
     <row r="12" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+      <c r="A12" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35"/>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="D14" s="2"/>
+      <c r="D14" s="1"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+      <c r="A15" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="7">
+      <c r="A17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35"/>
     <row r="19" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+      <c r="A19" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+      <c r="A20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+      <c r="A21" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+      <c r="A22" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
+      <c r="A23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="3">
         <v>2</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+      <c r="A24" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35"/>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="D26" s="2"/>
+      <c r="D26" s="1"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
+      <c r="A27" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
+      <c r="A28" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
+      <c r="A29" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B29" s="6">
+      <c r="B29" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
+      <c r="A31" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="3">
         <v>5</v>
       </c>
-      <c r="D31" s="4"/>
+      <c r="D31" s="2"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
+      <c r="A32" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D32" s="4"/>
+      <c r="D32" s="2"/>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
+      <c r="A33" s="3" t="s">
         <v>2</v>
       </c>
     </row>

--- a/CryoGrid/CryoGridCommunity_results/templates/automatic_loops/TILE_LOOP_NEXT.xlsx
+++ b/CryoGrid/CryoGridCommunity_results/templates/automatic_loops/TILE_LOOP_NEXT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Utilisateurs\pozsgayv\Documents\CryoGrid_VP_Workflow\CryoGrid\CryoGridCommunity_results\templates\automatic_loops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADB61598-A92B-4A32-8CD9-43D7CEF2028E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{687FA32F-57A1-4C33-82FD-12DC084E3F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="21">
   <si>
     <t>-------------------</t>
   </si>
@@ -69,19 +69,10 @@
     <t>END</t>
   </si>
   <si>
-    <t>OUT</t>
-  </si>
-  <si>
-    <t>tag</t>
-  </si>
-  <si>
     <t>FORCING_seb_mat</t>
   </si>
   <si>
     <t>OUT_last_timestep</t>
-  </si>
-  <si>
-    <t>save_timestep</t>
   </si>
   <si>
     <t>restart_OUT_last_timestep</t>
@@ -112,7 +103,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -125,13 +116,6 @@
       <color rgb="FF00CC00"/>
       <name val="Consolas"/>
       <family val="3"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF00B0F0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -160,14 +144,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -485,102 +468,102 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" outlineLevelRow="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.54296875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="19.54296875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="18.54296875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="16.81640625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="21.54296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="42.26953125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="9.7265625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="12.1796875" style="3" customWidth="1"/>
-    <col min="9" max="16384" width="8.81640625" style="3"/>
+    <col min="1" max="1" width="23.54296875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="19.54296875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="18.54296875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="16.81640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="21.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="42.26953125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="9.7265625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12.1796875" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="8.81640625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="3">
+      <c r="A3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35"/>
     <row r="5" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
+      <c r="D8" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
+    <row r="11" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="3">
-        <v>1</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
     </row>
     <row r="12" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -589,128 +572,87 @@
       <c r="D14" s="1"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="3">
+      <c r="A17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35"/>
     <row r="19" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>22</v>
+      <c r="B19" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>13</v>
+      <c r="B20" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" s="3" t="s">
+      <c r="C22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="3">
-        <v>2</v>
-      </c>
-      <c r="D23" s="3" t="s">
+      <c r="C23" s="2">
+        <v>1</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35"/>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="D26" s="1"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B29" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" s="3">
-        <v>5</v>
-      </c>
-      <c r="D31" s="2"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D32" s="2"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A33" s="3" t="s">
-        <v>2</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
